--- a/resources/国际化专业术语词典.xlsx
+++ b/resources/国际化专业术语词典.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="350" uniqueCount="350">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="362" uniqueCount="362">
   <si>
     <t/>
   </si>
@@ -36,19 +36,19 @@
     <t>资源池</t>
   </si>
   <si>
-    <t>resource pool</t>
+    <t>Resource Pool</t>
   </si>
   <si>
     <t>主机组</t>
   </si>
   <si>
-    <t>host group</t>
+    <t>Host Group</t>
   </si>
   <si>
     <t>主机</t>
   </si>
   <si>
-    <t>host</t>
+    <t>Host</t>
   </si>
   <si>
     <t>云主机</t>
@@ -69,7 +69,7 @@
     <t xml:space="preserve">控制台 </t>
   </si>
   <si>
-    <t>console</t>
+    <t>Console</t>
   </si>
   <si>
     <t>云主机备份</t>
@@ -87,7 +87,7 @@
     <t>软驱</t>
   </si>
   <si>
-    <t>floppy driver</t>
+    <t>Floppy Drive</t>
   </si>
   <si>
     <t>镜像</t>
@@ -120,25 +120,25 @@
     <t>全局内容库</t>
   </si>
   <si>
-    <t>GLobal Content Library</t>
+    <t>Global Content Library</t>
   </si>
   <si>
     <t>回收站</t>
   </si>
   <si>
-    <t>recycle bin</t>
+    <t>Recycle Bin</t>
   </si>
   <si>
     <t>分组</t>
   </si>
   <si>
-    <t>resource Group</t>
+    <t>Resource Group</t>
   </si>
   <si>
     <t>标签</t>
   </si>
   <si>
-    <t>resource label</t>
+    <t>Tag</t>
   </si>
   <si>
     <t>管理地址</t>
@@ -201,7 +201,7 @@
     <t>周期备份</t>
   </si>
   <si>
-    <t>scheduled backup</t>
+    <t>Scheduled Backup</t>
   </si>
   <si>
     <t>全量备份</t>
@@ -432,7 +432,7 @@
     <t>防火墙服务</t>
   </si>
   <si>
-    <t>FIrewall Service</t>
+    <t>Firewall Service</t>
   </si>
   <si>
     <t>网关</t>
@@ -456,7 +456,7 @@
     <t>组播</t>
   </si>
   <si>
-    <t>multicast</t>
+    <t>Multicast</t>
   </si>
   <si>
     <t>最大传输单元</t>
@@ -486,7 +486,7 @@
     <t>随机分配</t>
   </si>
   <si>
-    <t>random</t>
+    <t>Random</t>
   </si>
   <si>
     <t>顺序分配</t>
@@ -576,12 +576,69 @@
     <t>纯文本控制台</t>
   </si>
   <si>
-    <t>运维</t>
+    <t>Plain Text Console</t>
   </si>
   <si>
     <t>监控</t>
   </si>
   <si>
+    <t>健康检查</t>
+  </si>
+  <si>
+    <t>health check</t>
+  </si>
+  <si>
+    <t>	Monitoring</t>
+  </si>
+  <si>
+    <t>告警</t>
+  </si>
+  <si>
+    <t>alerts</t>
+  </si>
+  <si>
+    <t>使用率</t>
+  </si>
+  <si>
+    <t>usage</t>
+  </si>
+  <si>
+    <t>流速</t>
+  </si>
+  <si>
+    <t>throughput</t>
+  </si>
+  <si>
+    <t>包流速</t>
+  </si>
+  <si>
+    <t>packet rate</t>
+  </si>
+  <si>
+    <t>运行状态</t>
+  </si>
+  <si>
+    <t>status</t>
+  </si>
+  <si>
+    <t>已使用/未使用/总</t>
+  </si>
+  <si>
+    <t>used/free/total</t>
+  </si>
+  <si>
+    <t>阈值</t>
+  </si>
+  <si>
+    <t>Threshold</t>
+  </si>
+  <si>
+    <t>指标</t>
+  </si>
+  <si>
+    <t>Metrics</t>
+  </si>
+  <si>
     <t>前端</t>
   </si>
   <si>
@@ -612,7 +669,7 @@
     <t>取消</t>
   </si>
   <si>
-    <t>Cancle</t>
+    <t>Cancel</t>
   </si>
   <si>
     <t>重置</t>
@@ -834,235 +891,214 @@
     <t>运营</t>
   </si>
   <si>
+    <t>资源组织</t>
+  </si>
+  <si>
+    <t>Resource Organization</t>
+  </si>
+  <si>
     <t>可用区</t>
   </si>
   <si>
+    <t>Availability Zone</t>
+  </si>
+  <si>
+    <t>内置可用区</t>
+  </si>
+  <si>
+    <t>Built-in Availability Zone</t>
+  </si>
+  <si>
+    <t>物理位置</t>
+  </si>
+  <si>
+    <t>Physical Location</t>
+  </si>
+  <si>
     <t>虚拟数据中心</t>
   </si>
   <si>
+    <t>Virtual Data Center</t>
+  </si>
+  <si>
+    <t>配额模板管理</t>
+  </si>
+  <si>
+    <t>Quota Template Management</t>
+  </si>
+  <si>
+    <t>配额</t>
+  </si>
+  <si>
+    <t>Quota</t>
+  </si>
+  <si>
     <t>用户管理</t>
   </si>
   <si>
+    <t>User Management</t>
+  </si>
+  <si>
     <t>角色管理</t>
   </si>
   <si>
+    <t>Role Management</t>
+  </si>
+  <si>
     <t>用户组管理</t>
   </si>
   <si>
-    <t>资源组织</t>
+    <t>User Group Management</t>
   </si>
   <si>
     <t>任务</t>
   </si>
   <si>
+    <t>Task</t>
+  </si>
+  <si>
     <t>普通任务</t>
   </si>
   <si>
+    <t>General Task</t>
+  </si>
+  <si>
     <t>系统任务</t>
   </si>
   <si>
+    <t>System Task</t>
+  </si>
+  <si>
     <t>定时任务</t>
   </si>
   <si>
+    <t>Scheduled Task</t>
+  </si>
+  <si>
     <t>业务流程</t>
   </si>
   <si>
+    <t>Business Process</t>
+  </si>
+  <si>
     <t>订单管理</t>
   </si>
   <si>
+    <t>Order Management</t>
+  </si>
+  <si>
     <t>流程管理</t>
   </si>
   <si>
+    <t>Process Management</t>
+  </si>
+  <si>
     <t>业务统计</t>
   </si>
   <si>
+    <t>Business Statistics</t>
+  </si>
+  <si>
     <t>报表</t>
   </si>
   <si>
+    <t>Report</t>
+  </si>
+  <si>
     <t>资源报表</t>
   </si>
   <si>
+    <t>Resource Report</t>
+  </si>
+  <si>
     <t>费用报表</t>
   </si>
   <si>
+    <t>Cost Report</t>
+  </si>
+  <si>
     <t>业务报表</t>
   </si>
   <si>
+    <t>Business Report</t>
+  </si>
+  <si>
     <t>日志报表</t>
   </si>
   <si>
+    <t>Log Report</t>
+  </si>
+  <si>
     <t>费用与成本</t>
   </si>
   <si>
-    <t>组织账密</t>
+    <t>Expense and Cost</t>
   </si>
   <si>
     <t>组织账单</t>
   </si>
   <si>
+    <t>Organization Bill</t>
+  </si>
+  <si>
     <t>明细账单</t>
   </si>
   <si>
+    <t>Detailed Bill</t>
+  </si>
+  <si>
     <t>用量明细</t>
   </si>
   <si>
+    <t>Usage Details</t>
+  </si>
+  <si>
     <t>价格配置</t>
   </si>
   <si>
-    <t>Resource Organization</t>
-  </si>
-  <si>
-    <t>Availability Zone</t>
-  </si>
-  <si>
-    <t>Virtual Data Center</t>
-  </si>
-  <si>
-    <t>User Management</t>
-  </si>
-  <si>
-    <t>Role Management</t>
-  </si>
-  <si>
-    <t>User Group Management</t>
-  </si>
-  <si>
-    <t>Task</t>
-  </si>
-  <si>
-    <t>General Task</t>
-  </si>
-  <si>
-    <t>System Task</t>
-  </si>
-  <si>
-    <t>Scheduled Task</t>
-  </si>
-  <si>
-    <t>Business Process</t>
-  </si>
-  <si>
-    <t>Order Management</t>
-  </si>
-  <si>
-    <t>Process Management</t>
-  </si>
-  <si>
-    <t>Business Statistics</t>
-  </si>
-  <si>
-    <t>Report</t>
-  </si>
-  <si>
-    <t>Resource Report</t>
-  </si>
-  <si>
-    <t>Cost Report</t>
-  </si>
-  <si>
-    <t>Business Report</t>
-  </si>
-  <si>
-    <t>Log Report</t>
-  </si>
-  <si>
-    <t>Expense and Cost</t>
-  </si>
-  <si>
-    <t>Organization Bill</t>
-  </si>
-  <si>
-    <t>Detailed Bill</t>
-  </si>
-  <si>
-    <t>Usage Details</t>
-  </si>
-  <si>
     <t>Price Configuration</t>
   </si>
   <si>
-    <t>内置可用区</t>
-  </si>
-  <si>
-    <t>物理位置</t>
-  </si>
-  <si>
-    <t>配额模板管理</t>
-  </si>
-  <si>
-    <t>配额</t>
-  </si>
-  <si>
-    <t>Built-in Availability Zone</t>
-  </si>
-  <si>
-    <t>Physical Location</t>
-  </si>
-  <si>
-    <t>Quota Template Management</t>
-  </si>
-  <si>
-    <t>Quota</t>
-  </si>
-  <si>
-    <t>告警</t>
-  </si>
-  <si>
-    <t>alerts</t>
-  </si>
-  <si>
-    <t>健康检查</t>
-  </si>
-  <si>
-    <t>health check</t>
-  </si>
-  <si>
-    <t>使用率</t>
-  </si>
-  <si>
-    <t>usage</t>
-  </si>
-  <si>
-    <t>流速</t>
-  </si>
-  <si>
-    <t>throughput</t>
-  </si>
-  <si>
-    <t>运行状态</t>
-  </si>
-  <si>
-    <t>status</t>
-  </si>
-  <si>
-    <t>monitor</t>
-  </si>
-  <si>
-    <t>used/free/total</t>
-  </si>
-  <si>
-    <t>已使用/未使用/总</t>
-  </si>
-  <si>
-    <t>包流速</t>
-  </si>
-  <si>
-    <t>packet rate</t>
-  </si>
-  <si>
-    <t>阈值</t>
-  </si>
-  <si>
-    <t>Threshold</t>
-  </si>
-  <si>
-    <t>Metrics</t>
-  </si>
-  <si>
-    <t>指标</t>
-  </si>
-  <si>
-    <t>	Monitoring</t>
+    <t>Sequential</t>
+  </si>
+  <si>
+    <t>Health Check</t>
+  </si>
+  <si>
+    <t>Alerts</t>
+  </si>
+  <si>
+    <t>Usage</t>
+  </si>
+  <si>
+    <t>Throughput</t>
+  </si>
+  <si>
+    <t>Packet Rate</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>Used/Free/Total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Allocation </t>
+  </si>
+  <si>
+    <t>Advanced Configuration</t>
+  </si>
+  <si>
+    <t>Virtual NIC</t>
+  </si>
+  <si>
+    <t>Bare Metal Volume</t>
+  </si>
+  <si>
+    <t>Static Routing</t>
+  </si>
+  <si>
+    <t>Overcommit Ratio</t>
   </si>
 </sst>
 </file>
@@ -1127,7 +1163,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -1170,7 +1206,14 @@
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
-      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFFFFFFF"/>
+      </bottom>
     </border>
     <border>
       <left style="thin">
@@ -1182,23 +1225,15 @@
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
+      <bottom/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FFFFFFFF"/>
-      </bottom>
-    </border>
-    <border/>
   </borders>
   <cellStyleXfs>
     <xf fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1236,15 +1271,21 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf fontId="0" fillId="0" borderId="3" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf fontId="7" fillId="0" borderId="4" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="5" xfId="0">
+      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="5" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="3" xfId="0">
       <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0"/>
     </xf>
     <xf fontId="0" fillId="0" borderId="3" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="4" xfId="0">
-      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="4" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf fontId="0" fillId="0" borderId="1" xfId="0">
@@ -1259,23 +1300,11 @@
     <xf fontId="0" fillId="0" borderId="1" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf fontId="0" fillId="0" borderId="3" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf fontId="0" fillId="0" borderId="1" xfId="0">
       <alignment vertical="center"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="4" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="4" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf fontId="7" fillId="0" borderId="5" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf fontId="7" fillId="0" borderId="5" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="6" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf fontId="8" fillId="3" borderId="0" xfId="0">
       <alignment vertical="center"/>
@@ -1534,7 +1563,7 @@
     <col min="4" max="4" width="18.4844" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" s="26" customFormat="1">
+    <row r="1" spans="1:4" s="24" customFormat="1">
       <c r="A1" s="4" t="s">
         <v>1</v>
       </c>
@@ -1812,7 +1841,7 @@
         <v>50</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>51</v>
+        <v>361</v>
       </c>
       <c r="D23" s="5" t="s"/>
     </row>
@@ -1824,7 +1853,7 @@
         <v>52</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>53</v>
+        <v>356</v>
       </c>
       <c r="D24" s="5" t="s"/>
     </row>
@@ -1958,7 +1987,7 @@
         <v>75</v>
       </c>
       <c r="C35" s="8" t="s">
-        <v>76</v>
+        <v>359</v>
       </c>
       <c r="D35" s="5" t="s"/>
     </row>
@@ -2464,7 +2493,7 @@
         <v>158</v>
       </c>
       <c r="C77" s="5" t="s">
-        <v>159</v>
+        <v>348</v>
       </c>
       <c r="D77" s="5" t="s"/>
     </row>
@@ -2476,7 +2505,7 @@
         <v>160</v>
       </c>
       <c r="C78" s="5" t="s">
-        <v>161</v>
+        <v>360</v>
       </c>
       <c r="D78" s="5" t="s"/>
     </row>
@@ -2500,7 +2529,7 @@
         <v>164</v>
       </c>
       <c r="C80" s="5" t="s">
-        <v>165</v>
+        <v>358</v>
       </c>
       <c r="D80" s="5" t="s"/>
     </row>
@@ -2627,7 +2656,9 @@
       <c r="B90" s="5" t="s">
         <v>186</v>
       </c>
-      <c r="C90" s="5" t="s"/>
+      <c r="C90" s="5" t="s">
+        <v>187</v>
+      </c>
       <c r="D90" s="5" t="s"/>
     </row>
     <row r="91" spans="1:4">
@@ -2659,10 +2690,10 @@
         <v>188</v>
       </c>
       <c r="B95" s="11" t="s">
-        <v>332</v>
+        <v>189</v>
       </c>
       <c r="C95" s="11" t="s">
-        <v>333</v>
+        <v>349</v>
       </c>
       <c r="D95" s="11" t="s"/>
     </row>
@@ -2674,951 +2705,951 @@
         <v>188</v>
       </c>
       <c r="C96" s="11" t="s">
-        <v>349</v>
+        <v>191</v>
       </c>
       <c r="D96" s="11" t="s"/>
     </row>
     <row r="97" spans="1:4">
-      <c r="A97" s="22" t="s">
+      <c r="A97" s="12" t="s">
         <v>188</v>
       </c>
-      <c r="B97" s="22" t="s">
-        <v>330</v>
-      </c>
-      <c r="C97" s="22" t="s">
-        <v>331</v>
-      </c>
-      <c r="D97" s="22" t="s"/>
+      <c r="B97" s="12" t="s">
+        <v>192</v>
+      </c>
+      <c r="C97" s="12" t="s">
+        <v>350</v>
+      </c>
+      <c r="D97" s="12" t="s"/>
     </row>
     <row r="98" spans="1:4">
-      <c r="A98" s="22" t="s">
+      <c r="A98" s="12" t="s">
         <v>188</v>
       </c>
-      <c r="B98" s="22" t="s">
-        <v>334</v>
-      </c>
-      <c r="C98" s="22" t="s">
-        <v>335</v>
-      </c>
-      <c r="D98" s="22" t="s"/>
+      <c r="B98" s="12" t="s">
+        <v>194</v>
+      </c>
+      <c r="C98" s="12" t="s">
+        <v>351</v>
+      </c>
+      <c r="D98" s="12" t="s"/>
     </row>
     <row r="99" spans="1:4">
-      <c r="A99" s="22" t="s">
+      <c r="A99" s="12" t="s">
         <v>188</v>
       </c>
-      <c r="B99" s="22" t="s">
-        <v>336</v>
-      </c>
-      <c r="C99" s="22" t="s">
-        <v>337</v>
-      </c>
-      <c r="D99" s="22" t="s"/>
+      <c r="B99" s="12" t="s">
+        <v>196</v>
+      </c>
+      <c r="C99" s="12" t="s">
+        <v>352</v>
+      </c>
+      <c r="D99" s="12" t="s"/>
     </row>
     <row r="100" spans="1:4">
-      <c r="A100" s="22" t="s">
+      <c r="A100" s="12" t="s">
         <v>188</v>
       </c>
-      <c r="B100" s="22" t="s">
-        <v>343</v>
-      </c>
-      <c r="C100" s="22" t="s">
-        <v>344</v>
-      </c>
-      <c r="D100" s="22" t="s"/>
+      <c r="B100" s="12" t="s">
+        <v>198</v>
+      </c>
+      <c r="C100" s="12" t="s">
+        <v>353</v>
+      </c>
+      <c r="D100" s="12" t="s"/>
     </row>
     <row r="101" spans="1:4" ht="16.5" customHeight="1">
-      <c r="A101" s="22" t="s">
+      <c r="A101" s="12" t="s">
         <v>188</v>
       </c>
-      <c r="B101" s="22" t="s">
-        <v>338</v>
-      </c>
-      <c r="C101" s="22" t="s">
-        <v>339</v>
-      </c>
-      <c r="D101" s="22" t="s"/>
+      <c r="B101" s="12" t="s">
+        <v>200</v>
+      </c>
+      <c r="C101" s="12" t="s">
+        <v>354</v>
+      </c>
+      <c r="D101" s="12" t="s"/>
     </row>
     <row r="102" spans="1:4" ht="16.5" customHeight="1">
-      <c r="A102" s="22" t="s">
+      <c r="A102" s="12" t="s">
         <v>188</v>
       </c>
-      <c r="B102" s="22" t="s">
-        <v>342</v>
-      </c>
-      <c r="C102" s="22" t="s">
-        <v>341</v>
-      </c>
-      <c r="D102" s="22" t="s"/>
+      <c r="B102" s="12" t="s">
+        <v>202</v>
+      </c>
+      <c r="C102" s="12" t="s">
+        <v>355</v>
+      </c>
+      <c r="D102" s="12" t="s"/>
     </row>
     <row r="103" spans="1:4" ht="16.5" customHeight="1">
-      <c r="A103" s="22" t="s">
+      <c r="A103" s="12" t="s">
         <v>188</v>
       </c>
-      <c r="B103" s="24" t="s">
-        <v>345</v>
-      </c>
-      <c r="C103" s="24" t="s">
-        <v>346</v>
-      </c>
-      <c r="D103" s="22" t="s"/>
+      <c r="B103" s="13" t="s">
+        <v>204</v>
+      </c>
+      <c r="C103" s="13" t="s">
+        <v>205</v>
+      </c>
+      <c r="D103" s="12" t="s"/>
     </row>
     <row r="104" spans="1:4" ht="16.5" customHeight="1">
-      <c r="A104" s="22" t="s">
+      <c r="A104" s="12" t="s">
         <v>188</v>
       </c>
-      <c r="B104" s="22" t="s">
-        <v>348</v>
-      </c>
-      <c r="C104" s="22" t="s">
-        <v>347</v>
-      </c>
-      <c r="D104" s="22" t="s"/>
+      <c r="B104" s="12" t="s">
+        <v>206</v>
+      </c>
+      <c r="C104" s="12" t="s">
+        <v>207</v>
+      </c>
+      <c r="D104" s="12" t="s"/>
     </row>
     <row r="105" spans="1:4">
-      <c r="A105" s="22" t="s"/>
-      <c r="B105" s="22" t="s"/>
-      <c r="C105" s="22" t="s"/>
-      <c r="D105" s="22" t="s"/>
+      <c r="A105" s="12" t="s"/>
+      <c r="B105" s="12" t="s"/>
+      <c r="C105" s="12" t="s"/>
+      <c r="D105" s="12" t="s"/>
     </row>
     <row r="106" spans="1:4">
-      <c r="A106" s="12" t="s">
-        <v>189</v>
-      </c>
-      <c r="B106" s="12" t="s">
-        <v>190</v>
-      </c>
-      <c r="C106" s="12" t="s">
-        <v>191</v>
-      </c>
-      <c r="D106" s="13" t="s"/>
+      <c r="A106" s="14" t="s">
+        <v>208</v>
+      </c>
+      <c r="B106" s="14" t="s">
+        <v>209</v>
+      </c>
+      <c r="C106" s="14" t="s">
+        <v>210</v>
+      </c>
+      <c r="D106" s="15" t="s"/>
     </row>
     <row r="107" spans="1:4">
-      <c r="A107" s="14" t="s">
-        <v>189</v>
-      </c>
-      <c r="B107" s="14" t="s">
-        <v>192</v>
-      </c>
-      <c r="C107" s="14" t="s">
-        <v>193</v>
-      </c>
-      <c r="D107" s="15" t="s"/>
+      <c r="A107" s="16" t="s">
+        <v>208</v>
+      </c>
+      <c r="B107" s="16" t="s">
+        <v>211</v>
+      </c>
+      <c r="C107" s="16" t="s">
+        <v>212</v>
+      </c>
+      <c r="D107" s="17" t="s"/>
     </row>
     <row r="108" spans="1:4">
-      <c r="A108" s="16" t="s">
-        <v>189</v>
-      </c>
-      <c r="B108" s="16" t="s">
-        <v>194</v>
-      </c>
-      <c r="C108" s="16" t="s">
-        <v>195</v>
-      </c>
-      <c r="D108" s="17" t="s"/>
+      <c r="A108" s="18" t="s">
+        <v>208</v>
+      </c>
+      <c r="B108" s="18" t="s">
+        <v>213</v>
+      </c>
+      <c r="C108" s="18" t="s">
+        <v>214</v>
+      </c>
+      <c r="D108" s="19" t="s"/>
     </row>
     <row r="109" spans="1:4">
-      <c r="A109" s="16" t="s">
-        <v>189</v>
-      </c>
-      <c r="B109" s="16" t="s">
-        <v>196</v>
-      </c>
-      <c r="C109" s="16" t="s">
-        <v>197</v>
-      </c>
-      <c r="D109" s="17" t="s"/>
+      <c r="A109" s="18" t="s">
+        <v>208</v>
+      </c>
+      <c r="B109" s="18" t="s">
+        <v>215</v>
+      </c>
+      <c r="C109" s="18" t="s">
+        <v>216</v>
+      </c>
+      <c r="D109" s="19" t="s"/>
     </row>
     <row r="110" spans="1:4">
-      <c r="A110" s="16" t="s">
-        <v>189</v>
-      </c>
-      <c r="B110" s="16" t="s">
-        <v>198</v>
-      </c>
-      <c r="C110" s="16" t="s">
-        <v>199</v>
-      </c>
-      <c r="D110" s="17" t="s"/>
+      <c r="A110" s="18" t="s">
+        <v>208</v>
+      </c>
+      <c r="B110" s="18" t="s">
+        <v>217</v>
+      </c>
+      <c r="C110" s="18" t="s">
+        <v>218</v>
+      </c>
+      <c r="D110" s="19" t="s"/>
     </row>
     <row r="111" spans="1:4">
-      <c r="A111" s="16" t="s">
-        <v>189</v>
-      </c>
-      <c r="B111" s="16" t="s">
-        <v>200</v>
-      </c>
-      <c r="C111" s="18" t="s">
-        <v>201</v>
-      </c>
-      <c r="D111" s="17" t="s"/>
+      <c r="A111" s="18" t="s">
+        <v>208</v>
+      </c>
+      <c r="B111" s="18" t="s">
+        <v>219</v>
+      </c>
+      <c r="C111" s="20" t="s">
+        <v>220</v>
+      </c>
+      <c r="D111" s="19" t="s"/>
     </row>
     <row r="112" spans="1:4">
-      <c r="A112" s="16" t="s">
-        <v>189</v>
-      </c>
-      <c r="B112" s="16" t="s">
-        <v>202</v>
-      </c>
-      <c r="C112" s="16" t="s">
-        <v>203</v>
-      </c>
-      <c r="D112" s="17" t="s"/>
+      <c r="A112" s="18" t="s">
+        <v>208</v>
+      </c>
+      <c r="B112" s="18" t="s">
+        <v>221</v>
+      </c>
+      <c r="C112" s="18" t="s">
+        <v>222</v>
+      </c>
+      <c r="D112" s="19" t="s"/>
     </row>
     <row r="113" spans="1:4">
-      <c r="A113" s="16" t="s">
-        <v>189</v>
-      </c>
-      <c r="B113" s="16" t="s">
-        <v>204</v>
-      </c>
-      <c r="C113" s="16" t="s">
-        <v>205</v>
-      </c>
-      <c r="D113" s="17" t="s"/>
+      <c r="A113" s="18" t="s">
+        <v>208</v>
+      </c>
+      <c r="B113" s="18" t="s">
+        <v>223</v>
+      </c>
+      <c r="C113" s="18" t="s">
+        <v>224</v>
+      </c>
+      <c r="D113" s="19" t="s"/>
     </row>
     <row r="114" spans="1:4">
-      <c r="A114" s="16" t="s">
-        <v>189</v>
-      </c>
-      <c r="B114" s="16" t="s">
-        <v>206</v>
-      </c>
-      <c r="C114" s="16" t="s">
-        <v>207</v>
-      </c>
-      <c r="D114" s="17" t="s"/>
+      <c r="A114" s="18" t="s">
+        <v>208</v>
+      </c>
+      <c r="B114" s="18" t="s">
+        <v>225</v>
+      </c>
+      <c r="C114" s="18" t="s">
+        <v>226</v>
+      </c>
+      <c r="D114" s="19" t="s"/>
     </row>
     <row r="115" spans="1:4">
-      <c r="A115" s="16" t="s">
-        <v>189</v>
-      </c>
-      <c r="B115" s="16" t="s">
-        <v>208</v>
-      </c>
-      <c r="C115" s="16" t="s">
-        <v>209</v>
-      </c>
-      <c r="D115" s="17" t="s"/>
+      <c r="A115" s="18" t="s">
+        <v>208</v>
+      </c>
+      <c r="B115" s="18" t="s">
+        <v>227</v>
+      </c>
+      <c r="C115" s="18" t="s">
+        <v>228</v>
+      </c>
+      <c r="D115" s="19" t="s"/>
     </row>
     <row r="116" spans="1:4">
-      <c r="A116" s="16" t="s">
-        <v>189</v>
-      </c>
-      <c r="B116" s="16" t="s">
-        <v>210</v>
-      </c>
-      <c r="C116" s="16" t="s">
-        <v>211</v>
-      </c>
-      <c r="D116" s="17" t="s"/>
+      <c r="A116" s="18" t="s">
+        <v>208</v>
+      </c>
+      <c r="B116" s="18" t="s">
+        <v>229</v>
+      </c>
+      <c r="C116" s="18" t="s">
+        <v>230</v>
+      </c>
+      <c r="D116" s="19" t="s"/>
     </row>
     <row r="117" spans="1:4">
-      <c r="A117" s="16" t="s">
-        <v>189</v>
-      </c>
-      <c r="B117" s="16" t="s">
-        <v>212</v>
-      </c>
-      <c r="C117" s="16" t="s">
-        <v>213</v>
-      </c>
-      <c r="D117" s="17" t="s"/>
+      <c r="A117" s="18" t="s">
+        <v>208</v>
+      </c>
+      <c r="B117" s="18" t="s">
+        <v>231</v>
+      </c>
+      <c r="C117" s="18" t="s">
+        <v>232</v>
+      </c>
+      <c r="D117" s="19" t="s"/>
     </row>
     <row r="118" spans="1:4">
-      <c r="A118" s="16" t="s">
-        <v>189</v>
-      </c>
-      <c r="B118" s="16" t="s">
-        <v>214</v>
-      </c>
-      <c r="C118" s="16" t="s">
-        <v>215</v>
-      </c>
-      <c r="D118" s="17" t="s"/>
+      <c r="A118" s="18" t="s">
+        <v>208</v>
+      </c>
+      <c r="B118" s="18" t="s">
+        <v>233</v>
+      </c>
+      <c r="C118" s="18" t="s">
+        <v>234</v>
+      </c>
+      <c r="D118" s="19" t="s"/>
     </row>
     <row r="119" spans="1:4">
-      <c r="A119" s="16" t="s">
-        <v>189</v>
-      </c>
-      <c r="B119" s="16" t="s">
-        <v>216</v>
-      </c>
-      <c r="C119" s="16" t="s">
-        <v>217</v>
-      </c>
-      <c r="D119" s="17" t="s"/>
+      <c r="A119" s="18" t="s">
+        <v>208</v>
+      </c>
+      <c r="B119" s="18" t="s">
+        <v>235</v>
+      </c>
+      <c r="C119" s="18" t="s">
+        <v>236</v>
+      </c>
+      <c r="D119" s="19" t="s"/>
     </row>
     <row r="120" spans="1:4">
-      <c r="A120" s="16" t="s">
-        <v>189</v>
-      </c>
-      <c r="B120" s="16" t="s">
-        <v>218</v>
-      </c>
-      <c r="C120" s="16" t="s">
-        <v>219</v>
-      </c>
-      <c r="D120" s="17" t="s"/>
+      <c r="A120" s="18" t="s">
+        <v>208</v>
+      </c>
+      <c r="B120" s="18" t="s">
+        <v>237</v>
+      </c>
+      <c r="C120" s="18" t="s">
+        <v>238</v>
+      </c>
+      <c r="D120" s="19" t="s"/>
     </row>
     <row r="121" spans="1:4">
-      <c r="A121" s="16" t="s">
-        <v>189</v>
-      </c>
-      <c r="B121" s="16" t="s">
-        <v>220</v>
-      </c>
-      <c r="C121" s="16" t="s">
-        <v>221</v>
-      </c>
-      <c r="D121" s="17" t="s"/>
+      <c r="A121" s="18" t="s">
+        <v>208</v>
+      </c>
+      <c r="B121" s="18" t="s">
+        <v>239</v>
+      </c>
+      <c r="C121" s="18" t="s">
+        <v>240</v>
+      </c>
+      <c r="D121" s="19" t="s"/>
     </row>
     <row r="122" spans="1:4">
-      <c r="A122" s="16" t="s">
-        <v>189</v>
-      </c>
-      <c r="B122" s="16" t="s">
-        <v>222</v>
-      </c>
-      <c r="C122" s="16" t="s">
-        <v>223</v>
-      </c>
-      <c r="D122" s="17" t="s"/>
+      <c r="A122" s="18" t="s">
+        <v>208</v>
+      </c>
+      <c r="B122" s="18" t="s">
+        <v>241</v>
+      </c>
+      <c r="C122" s="18" t="s">
+        <v>242</v>
+      </c>
+      <c r="D122" s="19" t="s"/>
     </row>
     <row r="123" spans="1:4">
-      <c r="A123" s="16" t="s">
-        <v>189</v>
-      </c>
-      <c r="B123" s="16" t="s">
-        <v>224</v>
-      </c>
-      <c r="C123" s="16" t="s">
-        <v>225</v>
-      </c>
-      <c r="D123" s="17" t="s"/>
+      <c r="A123" s="18" t="s">
+        <v>208</v>
+      </c>
+      <c r="B123" s="18" t="s">
+        <v>243</v>
+      </c>
+      <c r="C123" s="18" t="s">
+        <v>244</v>
+      </c>
+      <c r="D123" s="19" t="s"/>
     </row>
     <row r="124" spans="1:4">
-      <c r="A124" s="16" t="s">
-        <v>189</v>
-      </c>
-      <c r="B124" s="16" t="s">
-        <v>226</v>
-      </c>
-      <c r="C124" s="16" t="s">
-        <v>227</v>
-      </c>
-      <c r="D124" s="17" t="s"/>
+      <c r="A124" s="18" t="s">
+        <v>208</v>
+      </c>
+      <c r="B124" s="18" t="s">
+        <v>245</v>
+      </c>
+      <c r="C124" s="18" t="s">
+        <v>246</v>
+      </c>
+      <c r="D124" s="19" t="s"/>
     </row>
     <row r="125" spans="1:4">
-      <c r="A125" s="16" t="s">
-        <v>189</v>
-      </c>
-      <c r="B125" s="16" t="s">
-        <v>228</v>
-      </c>
-      <c r="C125" s="16" t="s">
-        <v>229</v>
-      </c>
-      <c r="D125" s="17" t="s"/>
+      <c r="A125" s="18" t="s">
+        <v>208</v>
+      </c>
+      <c r="B125" s="18" t="s">
+        <v>247</v>
+      </c>
+      <c r="C125" s="18" t="s">
+        <v>248</v>
+      </c>
+      <c r="D125" s="19" t="s"/>
     </row>
     <row r="126" spans="1:4">
-      <c r="A126" s="16" t="s">
-        <v>189</v>
-      </c>
-      <c r="B126" s="16" t="s">
-        <v>230</v>
-      </c>
-      <c r="C126" s="16" t="s">
-        <v>221</v>
-      </c>
-      <c r="D126" s="17" t="s"/>
+      <c r="A126" s="18" t="s">
+        <v>208</v>
+      </c>
+      <c r="B126" s="18" t="s">
+        <v>249</v>
+      </c>
+      <c r="C126" s="18" t="s">
+        <v>240</v>
+      </c>
+      <c r="D126" s="19" t="s"/>
     </row>
     <row r="127" spans="1:4">
-      <c r="A127" s="16" t="s">
-        <v>189</v>
-      </c>
-      <c r="B127" s="16" t="s">
-        <v>231</v>
-      </c>
-      <c r="C127" s="16" t="s">
+      <c r="A127" s="18" t="s">
+        <v>208</v>
+      </c>
+      <c r="B127" s="18" t="s">
+        <v>250</v>
+      </c>
+      <c r="C127" s="18" t="s">
+        <v>251</v>
+      </c>
+      <c r="D127" s="21" t="s"/>
+    </row>
+    <row r="128" spans="1:4">
+      <c r="A128" s="18" t="s">
+        <v>208</v>
+      </c>
+      <c r="B128" s="18" t="s">
+        <v>252</v>
+      </c>
+      <c r="C128" s="18" t="s">
+        <v>253</v>
+      </c>
+      <c r="D128" s="21" t="s"/>
+    </row>
+    <row r="129" spans="1:4">
+      <c r="A129" s="18" t="s">
+        <v>208</v>
+      </c>
+      <c r="B129" s="18" t="s">
+        <v>254</v>
+      </c>
+      <c r="C129" s="18" t="s">
+        <v>255</v>
+      </c>
+      <c r="D129" s="21" t="s"/>
+    </row>
+    <row r="130" spans="1:4">
+      <c r="A130" s="18" t="s">
+        <v>208</v>
+      </c>
+      <c r="B130" s="18" t="s">
+        <v>256</v>
+      </c>
+      <c r="C130" s="18" t="s">
+        <v>257</v>
+      </c>
+      <c r="D130" s="21" t="s"/>
+    </row>
+    <row r="131" spans="1:4">
+      <c r="A131" s="18" t="s">
+        <v>208</v>
+      </c>
+      <c r="B131" s="18" t="s">
+        <v>258</v>
+      </c>
+      <c r="C131" s="18" t="s">
+        <v>259</v>
+      </c>
+      <c r="D131" s="19" t="s"/>
+    </row>
+    <row r="132" spans="1:4">
+      <c r="A132" s="18" t="s">
+        <v>208</v>
+      </c>
+      <c r="B132" s="18" t="s">
+        <v>260</v>
+      </c>
+      <c r="C132" s="18" t="s">
+        <v>261</v>
+      </c>
+      <c r="D132" s="19" t="s"/>
+    </row>
+    <row r="133" spans="1:4">
+      <c r="A133" s="18" t="s">
+        <v>208</v>
+      </c>
+      <c r="B133" s="18" t="s">
+        <v>262</v>
+      </c>
+      <c r="C133" s="18" t="s">
+        <v>263</v>
+      </c>
+      <c r="D133" s="19" t="s"/>
+    </row>
+    <row r="134" spans="1:4">
+      <c r="A134" s="18" t="s">
+        <v>208</v>
+      </c>
+      <c r="B134" s="18" t="s">
+        <v>264</v>
+      </c>
+      <c r="C134" s="18" t="s">
+        <v>265</v>
+      </c>
+      <c r="D134" s="19" t="s"/>
+    </row>
+    <row r="135" spans="1:4">
+      <c r="A135" s="18" t="s">
+        <v>208</v>
+      </c>
+      <c r="B135" s="18" t="s">
+        <v>266</v>
+      </c>
+      <c r="C135" s="18" t="s">
+        <v>267</v>
+      </c>
+      <c r="D135" s="19" t="s"/>
+    </row>
+    <row r="136" spans="1:4">
+      <c r="A136" s="18" t="s">
+        <v>208</v>
+      </c>
+      <c r="B136" s="18" t="s">
+        <v>268</v>
+      </c>
+      <c r="C136" s="18" t="s">
+        <v>269</v>
+      </c>
+      <c r="D136" s="19" t="s"/>
+    </row>
+    <row r="137" spans="1:4">
+      <c r="A137" s="18" t="s">
+        <v>208</v>
+      </c>
+      <c r="B137" s="18" t="s">
+        <v>270</v>
+      </c>
+      <c r="C137" s="18" t="s">
         <v>232</v>
       </c>
-      <c r="D127" s="19" t="s"/>
-    </row>
-    <row r="128" spans="1:4">
-      <c r="A128" s="16" t="s">
-        <v>189</v>
-      </c>
-      <c r="B128" s="16" t="s">
-        <v>233</v>
-      </c>
-      <c r="C128" s="16" t="s">
-        <v>234</v>
-      </c>
-      <c r="D128" s="19" t="s"/>
-    </row>
-    <row r="129" spans="1:4">
-      <c r="A129" s="16" t="s">
-        <v>189</v>
-      </c>
-      <c r="B129" s="16" t="s">
-        <v>235</v>
-      </c>
-      <c r="C129" s="16" t="s">
-        <v>236</v>
-      </c>
-      <c r="D129" s="19" t="s"/>
-    </row>
-    <row r="130" spans="1:4">
-      <c r="A130" s="16" t="s">
-        <v>189</v>
-      </c>
-      <c r="B130" s="16" t="s">
-        <v>237</v>
-      </c>
-      <c r="C130" s="16" t="s">
-        <v>238</v>
-      </c>
-      <c r="D130" s="19" t="s"/>
-    </row>
-    <row r="131" spans="1:4">
-      <c r="A131" s="16" t="s">
-        <v>189</v>
-      </c>
-      <c r="B131" s="16" t="s">
-        <v>239</v>
-      </c>
-      <c r="C131" s="16" t="s">
-        <v>240</v>
-      </c>
-      <c r="D131" s="17" t="s"/>
-    </row>
-    <row r="132" spans="1:4">
-      <c r="A132" s="16" t="s">
-        <v>189</v>
-      </c>
-      <c r="B132" s="16" t="s">
-        <v>241</v>
-      </c>
-      <c r="C132" s="16" t="s">
-        <v>242</v>
-      </c>
-      <c r="D132" s="17" t="s"/>
-    </row>
-    <row r="133" spans="1:4">
-      <c r="A133" s="16" t="s">
-        <v>189</v>
-      </c>
-      <c r="B133" s="16" t="s">
-        <v>243</v>
-      </c>
-      <c r="C133" s="16" t="s">
-        <v>244</v>
-      </c>
-      <c r="D133" s="17" t="s"/>
-    </row>
-    <row r="134" spans="1:4">
-      <c r="A134" s="16" t="s">
-        <v>189</v>
-      </c>
-      <c r="B134" s="16" t="s">
-        <v>245</v>
-      </c>
-      <c r="C134" s="16" t="s">
-        <v>246</v>
-      </c>
-      <c r="D134" s="17" t="s"/>
-    </row>
-    <row r="135" spans="1:4">
-      <c r="A135" s="16" t="s">
-        <v>189</v>
-      </c>
-      <c r="B135" s="16" t="s">
-        <v>247</v>
-      </c>
-      <c r="C135" s="16" t="s">
-        <v>248</v>
-      </c>
-      <c r="D135" s="17" t="s"/>
-    </row>
-    <row r="136" spans="1:4">
-      <c r="A136" s="16" t="s">
-        <v>189</v>
-      </c>
-      <c r="B136" s="16" t="s">
-        <v>249</v>
-      </c>
-      <c r="C136" s="16" t="s">
-        <v>250</v>
-      </c>
-      <c r="D136" s="17" t="s"/>
-    </row>
-    <row r="137" spans="1:4">
-      <c r="A137" s="16" t="s">
-        <v>189</v>
-      </c>
-      <c r="B137" s="16" t="s">
-        <v>251</v>
-      </c>
-      <c r="C137" s="16" t="s">
-        <v>213</v>
-      </c>
-      <c r="D137" s="17" t="s"/>
+      <c r="D137" s="19" t="s"/>
     </row>
     <row r="138" spans="1:4">
-      <c r="A138" s="16" t="s">
-        <v>189</v>
-      </c>
-      <c r="B138" s="16" t="s">
-        <v>252</v>
-      </c>
-      <c r="C138" s="16" t="s">
-        <v>253</v>
-      </c>
-      <c r="D138" s="17" t="s"/>
+      <c r="A138" s="18" t="s">
+        <v>208</v>
+      </c>
+      <c r="B138" s="18" t="s">
+        <v>271</v>
+      </c>
+      <c r="C138" s="18" t="s">
+        <v>272</v>
+      </c>
+      <c r="D138" s="19" t="s"/>
     </row>
     <row r="139" spans="1:4">
-      <c r="A139" s="16" t="s">
-        <v>189</v>
-      </c>
-      <c r="B139" s="16" t="s">
-        <v>254</v>
-      </c>
-      <c r="C139" s="16" t="s">
-        <v>255</v>
-      </c>
-      <c r="D139" s="17" t="s"/>
+      <c r="A139" s="18" t="s">
+        <v>208</v>
+      </c>
+      <c r="B139" s="18" t="s">
+        <v>273</v>
+      </c>
+      <c r="C139" s="18" t="s">
+        <v>274</v>
+      </c>
+      <c r="D139" s="19" t="s"/>
     </row>
     <row r="140" spans="1:4">
-      <c r="A140" s="16" t="s">
-        <v>189</v>
-      </c>
-      <c r="B140" s="16" t="s">
-        <v>256</v>
-      </c>
-      <c r="C140" s="16" t="s">
-        <v>257</v>
-      </c>
-      <c r="D140" s="17" t="s"/>
+      <c r="A140" s="18" t="s">
+        <v>208</v>
+      </c>
+      <c r="B140" s="18" t="s">
+        <v>275</v>
+      </c>
+      <c r="C140" s="18" t="s">
+        <v>276</v>
+      </c>
+      <c r="D140" s="19" t="s"/>
     </row>
     <row r="141" spans="1:4">
-      <c r="A141" s="16" t="s">
-        <v>189</v>
-      </c>
-      <c r="B141" s="16" t="s">
-        <v>258</v>
-      </c>
-      <c r="C141" s="16" t="s">
-        <v>259</v>
-      </c>
-      <c r="D141" s="17" t="s"/>
+      <c r="A141" s="18" t="s">
+        <v>208</v>
+      </c>
+      <c r="B141" s="18" t="s">
+        <v>277</v>
+      </c>
+      <c r="C141" s="18" t="s">
+        <v>278</v>
+      </c>
+      <c r="D141" s="19" t="s"/>
     </row>
     <row r="142" spans="1:4">
-      <c r="A142" s="16" t="s">
-        <v>189</v>
-      </c>
-      <c r="B142" s="16" t="s">
-        <v>260</v>
-      </c>
-      <c r="C142" s="16" t="s">
-        <v>261</v>
-      </c>
-      <c r="D142" s="17" t="s"/>
+      <c r="A142" s="18" t="s">
+        <v>208</v>
+      </c>
+      <c r="B142" s="18" t="s">
+        <v>279</v>
+      </c>
+      <c r="C142" s="18" t="s">
+        <v>280</v>
+      </c>
+      <c r="D142" s="19" t="s"/>
     </row>
     <row r="143" spans="1:4">
-      <c r="A143" s="16" t="s">
-        <v>189</v>
-      </c>
-      <c r="B143" s="16" t="s">
-        <v>262</v>
-      </c>
-      <c r="C143" s="16" t="s">
-        <v>263</v>
-      </c>
-      <c r="D143" s="17" t="s"/>
+      <c r="A143" s="18" t="s">
+        <v>208</v>
+      </c>
+      <c r="B143" s="18" t="s">
+        <v>281</v>
+      </c>
+      <c r="C143" s="18" t="s">
+        <v>282</v>
+      </c>
+      <c r="D143" s="19" t="s"/>
     </row>
     <row r="144" spans="1:4">
-      <c r="A144" s="16" t="s">
-        <v>189</v>
-      </c>
-      <c r="B144" s="16" t="s">
-        <v>264</v>
-      </c>
-      <c r="C144" s="16" t="s">
-        <v>265</v>
-      </c>
-      <c r="D144" s="17" t="s"/>
+      <c r="A144" s="18" t="s">
+        <v>208</v>
+      </c>
+      <c r="B144" s="18" t="s">
+        <v>283</v>
+      </c>
+      <c r="C144" s="18" t="s">
+        <v>284</v>
+      </c>
+      <c r="D144" s="19" t="s"/>
     </row>
     <row r="145" spans="1:4">
-      <c r="A145" s="16" t="s">
-        <v>189</v>
-      </c>
-      <c r="B145" s="16" t="s">
-        <v>266</v>
-      </c>
-      <c r="C145" s="16" t="s">
-        <v>267</v>
-      </c>
-      <c r="D145" s="17" t="s"/>
+      <c r="A145" s="18" t="s">
+        <v>208</v>
+      </c>
+      <c r="B145" s="18" t="s">
+        <v>285</v>
+      </c>
+      <c r="C145" s="18" t="s">
+        <v>286</v>
+      </c>
+      <c r="D145" s="19" t="s"/>
     </row>
     <row r="146" spans="1:4">
-      <c r="A146" s="16" t="s">
-        <v>189</v>
-      </c>
-      <c r="B146" s="16" t="s">
-        <v>268</v>
-      </c>
-      <c r="C146" s="16" t="s">
-        <v>269</v>
-      </c>
-      <c r="D146" s="17" t="s"/>
+      <c r="A146" s="18" t="s">
+        <v>208</v>
+      </c>
+      <c r="B146" s="18" t="s">
+        <v>287</v>
+      </c>
+      <c r="C146" s="18" t="s">
+        <v>288</v>
+      </c>
+      <c r="D146" s="19" t="s"/>
     </row>
     <row r="147" spans="1:4">
-      <c r="A147" s="14" t="s">
-        <v>189</v>
-      </c>
-      <c r="B147" s="14" t="s">
-        <v>270</v>
-      </c>
-      <c r="C147" s="14" t="s">
-        <v>271</v>
-      </c>
-      <c r="D147" s="21" t="s"/>
+      <c r="A147" s="16" t="s">
+        <v>208</v>
+      </c>
+      <c r="B147" s="16" t="s">
+        <v>289</v>
+      </c>
+      <c r="C147" s="16" t="s">
+        <v>357</v>
+      </c>
+      <c r="D147" s="22" t="s"/>
     </row>
     <row r="148" spans="1:4">
       <c r="A148" s="11" t="s">
-        <v>272</v>
-      </c>
-      <c r="B148" s="20" t="s">
-        <v>278</v>
-      </c>
-      <c r="C148" s="20" t="s">
-        <v>298</v>
-      </c>
-      <c r="D148" s="20" t="s"/>
+        <v>291</v>
+      </c>
+      <c r="B148" s="23" t="s">
+        <v>292</v>
+      </c>
+      <c r="C148" s="23" t="s">
+        <v>293</v>
+      </c>
+      <c r="D148" s="23" t="s"/>
     </row>
     <row r="149" spans="1:4">
       <c r="A149" s="11" t="s">
-        <v>272</v>
-      </c>
-      <c r="B149" s="20" t="s">
-        <v>273</v>
-      </c>
-      <c r="C149" s="20" t="s">
-        <v>299</v>
-      </c>
-      <c r="D149" s="20" t="s"/>
+        <v>291</v>
+      </c>
+      <c r="B149" s="23" t="s">
+        <v>294</v>
+      </c>
+      <c r="C149" s="23" t="s">
+        <v>295</v>
+      </c>
+      <c r="D149" s="23" t="s"/>
     </row>
     <row r="150" spans="1:4">
       <c r="A150" s="11" t="s">
-        <v>272</v>
-      </c>
-      <c r="B150" s="20" t="s">
-        <v>322</v>
-      </c>
-      <c r="C150" s="20" t="s">
-        <v>326</v>
-      </c>
-      <c r="D150" s="20" t="s"/>
+        <v>291</v>
+      </c>
+      <c r="B150" s="23" t="s">
+        <v>296</v>
+      </c>
+      <c r="C150" s="23" t="s">
+        <v>297</v>
+      </c>
+      <c r="D150" s="23" t="s"/>
     </row>
     <row r="151" spans="1:4">
       <c r="A151" s="11" t="s">
-        <v>272</v>
-      </c>
-      <c r="B151" s="20" t="s">
-        <v>323</v>
-      </c>
-      <c r="C151" s="20" t="s">
-        <v>327</v>
-      </c>
-      <c r="D151" s="20" t="s"/>
+        <v>291</v>
+      </c>
+      <c r="B151" s="23" t="s">
+        <v>298</v>
+      </c>
+      <c r="C151" s="23" t="s">
+        <v>299</v>
+      </c>
+      <c r="D151" s="23" t="s"/>
     </row>
     <row r="152" spans="1:4">
       <c r="A152" s="11" t="s">
-        <v>272</v>
-      </c>
-      <c r="B152" s="20" t="s">
-        <v>274</v>
-      </c>
-      <c r="C152" s="20" t="s">
+        <v>291</v>
+      </c>
+      <c r="B152" s="23" t="s">
         <v>300</v>
       </c>
-      <c r="D152" s="20" t="s"/>
+      <c r="C152" s="23" t="s">
+        <v>301</v>
+      </c>
+      <c r="D152" s="23" t="s"/>
     </row>
     <row r="153" spans="1:4">
       <c r="A153" s="11" t="s">
-        <v>272</v>
-      </c>
-      <c r="B153" s="20" t="s">
-        <v>324</v>
-      </c>
-      <c r="C153" s="20" t="s">
-        <v>328</v>
-      </c>
-      <c r="D153" s="20" t="s"/>
+        <v>291</v>
+      </c>
+      <c r="B153" s="23" t="s">
+        <v>302</v>
+      </c>
+      <c r="C153" s="23" t="s">
+        <v>303</v>
+      </c>
+      <c r="D153" s="23" t="s"/>
     </row>
     <row r="154" spans="1:4">
       <c r="A154" s="11" t="s">
-        <v>272</v>
-      </c>
-      <c r="B154" s="20" t="s">
-        <v>325</v>
-      </c>
-      <c r="C154" s="20" t="s">
-        <v>329</v>
-      </c>
-      <c r="D154" s="20" t="s"/>
+        <v>291</v>
+      </c>
+      <c r="B154" s="23" t="s">
+        <v>304</v>
+      </c>
+      <c r="C154" s="23" t="s">
+        <v>305</v>
+      </c>
+      <c r="D154" s="23" t="s"/>
     </row>
     <row r="155" spans="1:4">
       <c r="A155" s="11" t="s">
-        <v>272</v>
-      </c>
-      <c r="B155" s="20" t="s">
-        <v>275</v>
-      </c>
-      <c r="C155" s="20" t="s">
-        <v>301</v>
-      </c>
-      <c r="D155" s="20" t="s"/>
+        <v>291</v>
+      </c>
+      <c r="B155" s="23" t="s">
+        <v>306</v>
+      </c>
+      <c r="C155" s="23" t="s">
+        <v>307</v>
+      </c>
+      <c r="D155" s="23" t="s"/>
     </row>
     <row r="156" spans="1:4">
       <c r="A156" s="11" t="s">
-        <v>272</v>
-      </c>
-      <c r="B156" s="20" t="s">
-        <v>276</v>
-      </c>
-      <c r="C156" s="20" t="s">
-        <v>302</v>
-      </c>
-      <c r="D156" s="20" t="s"/>
+        <v>291</v>
+      </c>
+      <c r="B156" s="23" t="s">
+        <v>308</v>
+      </c>
+      <c r="C156" s="23" t="s">
+        <v>309</v>
+      </c>
+      <c r="D156" s="23" t="s"/>
     </row>
     <row r="157" spans="1:4">
       <c r="A157" s="11" t="s">
-        <v>272</v>
-      </c>
-      <c r="B157" s="20" t="s">
-        <v>277</v>
-      </c>
-      <c r="C157" s="20" t="s">
-        <v>303</v>
-      </c>
-      <c r="D157" s="20" t="s"/>
+        <v>291</v>
+      </c>
+      <c r="B157" s="23" t="s">
+        <v>310</v>
+      </c>
+      <c r="C157" s="23" t="s">
+        <v>311</v>
+      </c>
+      <c r="D157" s="23" t="s"/>
     </row>
     <row r="158" spans="1:4">
       <c r="A158" s="11" t="s">
-        <v>272</v>
-      </c>
-      <c r="B158" s="20" t="s">
-        <v>279</v>
-      </c>
-      <c r="C158" s="20" t="s">
-        <v>304</v>
-      </c>
-      <c r="D158" s="20" t="s"/>
+        <v>291</v>
+      </c>
+      <c r="B158" s="23" t="s">
+        <v>312</v>
+      </c>
+      <c r="C158" s="23" t="s">
+        <v>313</v>
+      </c>
+      <c r="D158" s="23" t="s"/>
     </row>
     <row r="159" spans="1:4">
       <c r="A159" s="11" t="s">
-        <v>272</v>
-      </c>
-      <c r="B159" s="20" t="s">
-        <v>280</v>
-      </c>
-      <c r="C159" s="20" t="s">
-        <v>305</v>
-      </c>
-      <c r="D159" s="20" t="s"/>
+        <v>291</v>
+      </c>
+      <c r="B159" s="23" t="s">
+        <v>314</v>
+      </c>
+      <c r="C159" s="23" t="s">
+        <v>315</v>
+      </c>
+      <c r="D159" s="23" t="s"/>
     </row>
     <row r="160" spans="1:4">
       <c r="A160" s="11" t="s">
-        <v>272</v>
-      </c>
-      <c r="B160" s="20" t="s">
-        <v>281</v>
-      </c>
-      <c r="C160" s="20" t="s">
-        <v>306</v>
-      </c>
-      <c r="D160" s="20" t="s"/>
+        <v>291</v>
+      </c>
+      <c r="B160" s="23" t="s">
+        <v>316</v>
+      </c>
+      <c r="C160" s="23" t="s">
+        <v>317</v>
+      </c>
+      <c r="D160" s="23" t="s"/>
     </row>
     <row r="161" spans="1:4">
       <c r="A161" s="11" t="s">
-        <v>272</v>
-      </c>
-      <c r="B161" s="20" t="s">
-        <v>282</v>
-      </c>
-      <c r="C161" s="20" t="s">
-        <v>307</v>
-      </c>
-      <c r="D161" s="20" t="s"/>
+        <v>291</v>
+      </c>
+      <c r="B161" s="23" t="s">
+        <v>318</v>
+      </c>
+      <c r="C161" s="23" t="s">
+        <v>319</v>
+      </c>
+      <c r="D161" s="23" t="s"/>
     </row>
     <row r="162" spans="1:4">
       <c r="A162" s="11" t="s">
-        <v>272</v>
-      </c>
-      <c r="B162" s="20" t="s">
-        <v>283</v>
-      </c>
-      <c r="C162" s="20" t="s">
-        <v>308</v>
-      </c>
-      <c r="D162" s="20" t="s"/>
+        <v>291</v>
+      </c>
+      <c r="B162" s="23" t="s">
+        <v>320</v>
+      </c>
+      <c r="C162" s="23" t="s">
+        <v>321</v>
+      </c>
+      <c r="D162" s="23" t="s"/>
     </row>
     <row r="163" spans="1:4">
       <c r="A163" s="11" t="s">
-        <v>272</v>
-      </c>
-      <c r="B163" s="20" t="s">
-        <v>284</v>
-      </c>
-      <c r="C163" s="20" t="s">
-        <v>309</v>
-      </c>
-      <c r="D163" s="20" t="s"/>
+        <v>291</v>
+      </c>
+      <c r="B163" s="23" t="s">
+        <v>322</v>
+      </c>
+      <c r="C163" s="23" t="s">
+        <v>323</v>
+      </c>
+      <c r="D163" s="23" t="s"/>
     </row>
     <row r="164" spans="1:4">
       <c r="A164" s="11" t="s">
-        <v>272</v>
-      </c>
-      <c r="B164" s="20" t="s">
-        <v>285</v>
-      </c>
-      <c r="C164" s="20" t="s">
-        <v>310</v>
-      </c>
-      <c r="D164" s="20" t="s"/>
+        <v>291</v>
+      </c>
+      <c r="B164" s="23" t="s">
+        <v>324</v>
+      </c>
+      <c r="C164" s="23" t="s">
+        <v>325</v>
+      </c>
+      <c r="D164" s="23" t="s"/>
     </row>
     <row r="165" spans="1:4">
       <c r="A165" s="11" t="s">
-        <v>272</v>
-      </c>
-      <c r="B165" s="20" t="s">
-        <v>286</v>
-      </c>
-      <c r="C165" s="20" t="s">
-        <v>311</v>
-      </c>
-      <c r="D165" s="20" t="s"/>
+        <v>291</v>
+      </c>
+      <c r="B165" s="23" t="s">
+        <v>326</v>
+      </c>
+      <c r="C165" s="23" t="s">
+        <v>327</v>
+      </c>
+      <c r="D165" s="23" t="s"/>
     </row>
     <row r="166" spans="1:4">
       <c r="A166" s="11" t="s">
-        <v>272</v>
-      </c>
-      <c r="B166" s="20" t="s">
-        <v>287</v>
-      </c>
-      <c r="C166" s="20" t="s">
-        <v>312</v>
-      </c>
-      <c r="D166" s="20" t="s"/>
+        <v>291</v>
+      </c>
+      <c r="B166" s="23" t="s">
+        <v>328</v>
+      </c>
+      <c r="C166" s="23" t="s">
+        <v>329</v>
+      </c>
+      <c r="D166" s="23" t="s"/>
     </row>
     <row r="167" spans="1:4">
       <c r="A167" s="11" t="s">
-        <v>272</v>
-      </c>
-      <c r="B167" s="20" t="s">
-        <v>288</v>
-      </c>
-      <c r="C167" s="20" t="s">
-        <v>313</v>
-      </c>
-      <c r="D167" s="20" t="s"/>
+        <v>291</v>
+      </c>
+      <c r="B167" s="23" t="s">
+        <v>330</v>
+      </c>
+      <c r="C167" s="23" t="s">
+        <v>331</v>
+      </c>
+      <c r="D167" s="23" t="s"/>
     </row>
     <row r="168" spans="1:4">
       <c r="A168" s="11" t="s">
-        <v>272</v>
-      </c>
-      <c r="B168" s="20" t="s">
-        <v>289</v>
-      </c>
-      <c r="C168" s="20" t="s">
-        <v>314</v>
-      </c>
-      <c r="D168" s="20" t="s"/>
+        <v>291</v>
+      </c>
+      <c r="B168" s="23" t="s">
+        <v>332</v>
+      </c>
+      <c r="C168" s="23" t="s">
+        <v>333</v>
+      </c>
+      <c r="D168" s="23" t="s"/>
     </row>
     <row r="169" spans="1:4">
       <c r="A169" s="11" t="s">
-        <v>272</v>
-      </c>
-      <c r="B169" s="20" t="s">
-        <v>290</v>
-      </c>
-      <c r="C169" s="20" t="s">
-        <v>315</v>
-      </c>
-      <c r="D169" s="20" t="s"/>
+        <v>291</v>
+      </c>
+      <c r="B169" s="23" t="s">
+        <v>334</v>
+      </c>
+      <c r="C169" s="23" t="s">
+        <v>335</v>
+      </c>
+      <c r="D169" s="23" t="s"/>
     </row>
     <row r="170" spans="1:4">
       <c r="A170" s="11" t="s">
-        <v>272</v>
-      </c>
-      <c r="B170" s="20" t="s">
         <v>291</v>
       </c>
-      <c r="C170" s="20" t="s">
-        <v>316</v>
-      </c>
-      <c r="D170" s="20" t="s"/>
+      <c r="B170" s="23" t="s">
+        <v>336</v>
+      </c>
+      <c r="C170" s="23" t="s">
+        <v>337</v>
+      </c>
+      <c r="D170" s="23" t="s"/>
     </row>
     <row r="171" spans="1:4">
       <c r="A171" s="11" t="s">
-        <v>272</v>
-      </c>
-      <c r="B171" s="20" t="s">
-        <v>292</v>
-      </c>
-      <c r="C171" s="20" t="s">
-        <v>317</v>
-      </c>
-      <c r="D171" s="20" t="s"/>
+        <v>291</v>
+      </c>
+      <c r="B171" s="23" t="s">
+        <v>338</v>
+      </c>
+      <c r="C171" s="23" t="s">
+        <v>339</v>
+      </c>
+      <c r="D171" s="23" t="s"/>
     </row>
     <row r="172" spans="1:4">
       <c r="A172" s="11" t="s">
-        <v>272</v>
-      </c>
-      <c r="B172" s="20" t="s">
-        <v>294</v>
-      </c>
-      <c r="C172" s="20" t="s">
-        <v>318</v>
-      </c>
-      <c r="D172" s="20" t="s"/>
+        <v>291</v>
+      </c>
+      <c r="B172" s="23" t="s">
+        <v>340</v>
+      </c>
+      <c r="C172" s="23" t="s">
+        <v>341</v>
+      </c>
+      <c r="D172" s="23" t="s"/>
     </row>
     <row r="173" spans="1:4">
       <c r="A173" s="11" t="s">
-        <v>272</v>
-      </c>
-      <c r="B173" s="20" t="s">
-        <v>295</v>
-      </c>
-      <c r="C173" s="20" t="s">
-        <v>319</v>
-      </c>
-      <c r="D173" s="20" t="s"/>
+        <v>291</v>
+      </c>
+      <c r="B173" s="23" t="s">
+        <v>342</v>
+      </c>
+      <c r="C173" s="23" t="s">
+        <v>343</v>
+      </c>
+      <c r="D173" s="23" t="s"/>
     </row>
     <row r="174" spans="1:4">
       <c r="A174" s="11" t="s">
-        <v>272</v>
-      </c>
-      <c r="B174" s="20" t="s">
-        <v>296</v>
-      </c>
-      <c r="C174" s="20" t="s">
-        <v>320</v>
-      </c>
-      <c r="D174" s="20" t="s"/>
+        <v>291</v>
+      </c>
+      <c r="B174" s="23" t="s">
+        <v>344</v>
+      </c>
+      <c r="C174" s="23" t="s">
+        <v>345</v>
+      </c>
+      <c r="D174" s="23" t="s"/>
     </row>
     <row r="175" spans="1:4">
       <c r="A175" s="11" t="s">
-        <v>272</v>
-      </c>
-      <c r="B175" s="20" t="s">
-        <v>297</v>
-      </c>
-      <c r="C175" s="20" t="s">
-        <v>321</v>
-      </c>
-      <c r="D175" s="20" t="s"/>
+        <v>291</v>
+      </c>
+      <c r="B175" s="23" t="s">
+        <v>346</v>
+      </c>
+      <c r="C175" s="23" t="s">
+        <v>347</v>
+      </c>
+      <c r="D175" s="23" t="s"/>
     </row>
   </sheetData>
 </worksheet>

--- a/resources/国际化专业术语词典.xlsx
+++ b/resources/国际化专业术语词典.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="362" uniqueCount="362">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="369" uniqueCount="369">
   <si>
     <t/>
   </si>
@@ -1099,6 +1099,27 @@
   </si>
   <si>
     <t>Overcommit Ratio</t>
+  </si>
+  <si>
+    <t>NAT Gateway</t>
+  </si>
+  <si>
+    <t>NAT64 Gateway</t>
+  </si>
+  <si>
+    <t>Security Group</t>
+  </si>
+  <si>
+    <t>Peering Connection</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>Router</t>
+  </si>
+  <si>
+    <t>Load Balancer</t>
   </si>
 </sst>
 </file>
@@ -2147,7 +2168,7 @@
       </c>
       <c r="D48" s="5" t="s"/>
     </row>
-    <row r="49" spans="1:4">
+    <row r="49" spans="1:7">
       <c r="A49" s="5" t="s">
         <v>101</v>
       </c>
@@ -2159,6 +2180,9 @@
       </c>
       <c r="D49" s="5" t="s">
         <v>104</v>
+      </c>
+      <c r="G49" t="s">
+        <v>366</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2193,7 +2217,7 @@
         <v>109</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>110</v>
+        <v>362</v>
       </c>
       <c r="D52" s="5" t="s"/>
     </row>
@@ -2205,7 +2229,7 @@
         <v>111</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>112</v>
+        <v>363</v>
       </c>
       <c r="D53" s="5" t="s"/>
     </row>
@@ -2217,7 +2241,7 @@
         <v>113</v>
       </c>
       <c r="C54" s="5" t="s">
-        <v>114</v>
+        <v>365</v>
       </c>
       <c r="D54" s="5" t="s"/>
     </row>
@@ -2229,7 +2253,7 @@
         <v>115</v>
       </c>
       <c r="C55" s="5" t="s">
-        <v>116</v>
+        <v>364</v>
       </c>
       <c r="D55" s="5" t="s"/>
     </row>
@@ -2265,7 +2289,7 @@
         <v>121</v>
       </c>
       <c r="C58" s="5" t="s">
-        <v>122</v>
+        <v>367</v>
       </c>
       <c r="D58" s="5" t="s"/>
     </row>
@@ -2289,7 +2313,7 @@
         <v>125</v>
       </c>
       <c r="C60" s="5" t="s">
-        <v>126</v>
+        <v>368</v>
       </c>
       <c r="D60" s="5" t="s"/>
     </row>

--- a/resources/国际化专业术语词典.xlsx
+++ b/resources/国际化专业术语词典.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="369" uniqueCount="369">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="370" uniqueCount="370">
   <si>
     <t/>
   </si>
@@ -1120,6 +1120,9 @@
   </si>
   <si>
     <t>Load Balancer</t>
+  </si>
+  <si>
+    <t>VDC</t>
   </si>
 </sst>
 </file>
@@ -3397,7 +3400,9 @@
       <c r="C152" s="23" t="s">
         <v>301</v>
       </c>
-      <c r="D152" s="23" t="s"/>
+      <c r="D152" s="23" t="s">
+        <v>369</v>
+      </c>
     </row>
     <row r="153" spans="1:4">
       <c r="A153" s="11" t="s">

--- a/resources/国际化专业术语词典.xlsx
+++ b/resources/国际化专业术语词典.xlsx
@@ -1579,7 +1579,7 @@
   <sheetPr>
     <tabColor/>
   </sheetPr>
-  <dimension ref="D175"/>
+  <dimension ref="D174"/>
   <sheetFormatPr baseColWidth="13" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="2" max="2" width="26.8438" customWidth="1"/>
@@ -3203,10 +3203,10 @@
         <v>208</v>
       </c>
       <c r="B136" s="18" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="C136" s="18" t="s">
-        <v>269</v>
+        <v>232</v>
       </c>
       <c r="D136" s="19" t="s"/>
     </row>
@@ -3215,10 +3215,10 @@
         <v>208</v>
       </c>
       <c r="B137" s="18" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C137" s="18" t="s">
-        <v>232</v>
+        <v>272</v>
       </c>
       <c r="D137" s="19" t="s"/>
     </row>
@@ -3227,10 +3227,10 @@
         <v>208</v>
       </c>
       <c r="B138" s="18" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="C138" s="18" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="D138" s="19" t="s"/>
     </row>
@@ -3239,10 +3239,10 @@
         <v>208</v>
       </c>
       <c r="B139" s="18" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="C139" s="18" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="D139" s="19" t="s"/>
     </row>
@@ -3251,10 +3251,10 @@
         <v>208</v>
       </c>
       <c r="B140" s="18" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="C140" s="18" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="D140" s="19" t="s"/>
     </row>
@@ -3263,10 +3263,10 @@
         <v>208</v>
       </c>
       <c r="B141" s="18" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="C141" s="18" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="D141" s="19" t="s"/>
     </row>
@@ -3275,10 +3275,10 @@
         <v>208</v>
       </c>
       <c r="B142" s="18" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="C142" s="18" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="D142" s="19" t="s"/>
     </row>
@@ -3287,10 +3287,10 @@
         <v>208</v>
       </c>
       <c r="B143" s="18" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="C143" s="18" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="D143" s="19" t="s"/>
     </row>
@@ -3299,10 +3299,10 @@
         <v>208</v>
       </c>
       <c r="B144" s="18" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="C144" s="18" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="D144" s="19" t="s"/>
     </row>
@@ -3311,46 +3311,46 @@
         <v>208</v>
       </c>
       <c r="B145" s="18" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="C145" s="18" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="D145" s="19" t="s"/>
     </row>
     <row r="146" spans="1:4">
-      <c r="A146" s="18" t="s">
-        <v>208</v>
-      </c>
-      <c r="B146" s="18" t="s">
-        <v>287</v>
-      </c>
-      <c r="C146" s="18" t="s">
-        <v>288</v>
-      </c>
-      <c r="D146" s="19" t="s"/>
+      <c r="A146" s="16" t="s">
+        <v>208</v>
+      </c>
+      <c r="B146" s="16" t="s">
+        <v>289</v>
+      </c>
+      <c r="C146" s="16" t="s">
+        <v>357</v>
+      </c>
+      <c r="D146" s="22" t="s"/>
     </row>
     <row r="147" spans="1:4">
-      <c r="A147" s="16" t="s">
-        <v>208</v>
-      </c>
-      <c r="B147" s="16" t="s">
-        <v>289</v>
-      </c>
-      <c r="C147" s="16" t="s">
-        <v>357</v>
-      </c>
-      <c r="D147" s="22" t="s"/>
+      <c r="A147" s="11" t="s">
+        <v>291</v>
+      </c>
+      <c r="B147" s="23" t="s">
+        <v>292</v>
+      </c>
+      <c r="C147" s="23" t="s">
+        <v>293</v>
+      </c>
+      <c r="D147" s="23" t="s"/>
     </row>
     <row r="148" spans="1:4">
       <c r="A148" s="11" t="s">
         <v>291</v>
       </c>
       <c r="B148" s="23" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="C148" s="23" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="D148" s="23" t="s"/>
     </row>
@@ -3359,10 +3359,10 @@
         <v>291</v>
       </c>
       <c r="B149" s="23" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="C149" s="23" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="D149" s="23" t="s"/>
     </row>
@@ -3371,10 +3371,10 @@
         <v>291</v>
       </c>
       <c r="B150" s="23" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="C150" s="23" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="D150" s="23" t="s"/>
     </row>
@@ -3383,36 +3383,36 @@
         <v>291</v>
       </c>
       <c r="B151" s="23" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="C151" s="23" t="s">
-        <v>299</v>
-      </c>
-      <c r="D151" s="23" t="s"/>
+        <v>301</v>
+      </c>
+      <c r="D151" s="23" t="s">
+        <v>369</v>
+      </c>
     </row>
     <row r="152" spans="1:4">
       <c r="A152" s="11" t="s">
         <v>291</v>
       </c>
       <c r="B152" s="23" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="C152" s="23" t="s">
-        <v>301</v>
-      </c>
-      <c r="D152" s="23" t="s">
-        <v>369</v>
-      </c>
+        <v>303</v>
+      </c>
+      <c r="D152" s="23" t="s"/>
     </row>
     <row r="153" spans="1:4">
       <c r="A153" s="11" t="s">
         <v>291</v>
       </c>
       <c r="B153" s="23" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="C153" s="23" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="D153" s="23" t="s"/>
     </row>
@@ -3421,10 +3421,10 @@
         <v>291</v>
       </c>
       <c r="B154" s="23" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="C154" s="23" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="D154" s="23" t="s"/>
     </row>
@@ -3433,10 +3433,10 @@
         <v>291</v>
       </c>
       <c r="B155" s="23" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="C155" s="23" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="D155" s="23" t="s"/>
     </row>
@@ -3445,10 +3445,10 @@
         <v>291</v>
       </c>
       <c r="B156" s="23" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="C156" s="23" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="D156" s="23" t="s"/>
     </row>
@@ -3457,10 +3457,10 @@
         <v>291</v>
       </c>
       <c r="B157" s="23" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="C157" s="23" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="D157" s="23" t="s"/>
     </row>
@@ -3469,10 +3469,10 @@
         <v>291</v>
       </c>
       <c r="B158" s="23" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="C158" s="23" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="D158" s="23" t="s"/>
     </row>
@@ -3481,10 +3481,10 @@
         <v>291</v>
       </c>
       <c r="B159" s="23" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="C159" s="23" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="D159" s="23" t="s"/>
     </row>
@@ -3493,10 +3493,10 @@
         <v>291</v>
       </c>
       <c r="B160" s="23" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="C160" s="23" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="D160" s="23" t="s"/>
     </row>
@@ -3505,10 +3505,10 @@
         <v>291</v>
       </c>
       <c r="B161" s="23" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="C161" s="23" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="D161" s="23" t="s"/>
     </row>
@@ -3517,10 +3517,10 @@
         <v>291</v>
       </c>
       <c r="B162" s="23" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="C162" s="23" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="D162" s="23" t="s"/>
     </row>
@@ -3529,10 +3529,10 @@
         <v>291</v>
       </c>
       <c r="B163" s="23" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="C163" s="23" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="D163" s="23" t="s"/>
     </row>
@@ -3541,10 +3541,10 @@
         <v>291</v>
       </c>
       <c r="B164" s="23" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="C164" s="23" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="D164" s="23" t="s"/>
     </row>
@@ -3553,10 +3553,10 @@
         <v>291</v>
       </c>
       <c r="B165" s="23" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="C165" s="23" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="D165" s="23" t="s"/>
     </row>
@@ -3565,10 +3565,10 @@
         <v>291</v>
       </c>
       <c r="B166" s="23" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="C166" s="23" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="D166" s="23" t="s"/>
     </row>
@@ -3577,10 +3577,10 @@
         <v>291</v>
       </c>
       <c r="B167" s="23" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="C167" s="23" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="D167" s="23" t="s"/>
     </row>
@@ -3589,10 +3589,10 @@
         <v>291</v>
       </c>
       <c r="B168" s="23" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="C168" s="23" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="D168" s="23" t="s"/>
     </row>
@@ -3601,10 +3601,10 @@
         <v>291</v>
       </c>
       <c r="B169" s="23" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="C169" s="23" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="D169" s="23" t="s"/>
     </row>
@@ -3613,10 +3613,10 @@
         <v>291</v>
       </c>
       <c r="B170" s="23" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="C170" s="23" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="D170" s="23" t="s"/>
     </row>
@@ -3625,10 +3625,10 @@
         <v>291</v>
       </c>
       <c r="B171" s="23" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="C171" s="23" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="D171" s="23" t="s"/>
     </row>
@@ -3637,10 +3637,10 @@
         <v>291</v>
       </c>
       <c r="B172" s="23" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="C172" s="23" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="D172" s="23" t="s"/>
     </row>
@@ -3649,10 +3649,10 @@
         <v>291</v>
       </c>
       <c r="B173" s="23" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="C173" s="23" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="D173" s="23" t="s"/>
     </row>
@@ -3661,24 +3661,12 @@
         <v>291</v>
       </c>
       <c r="B174" s="23" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="C174" s="23" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="D174" s="23" t="s"/>
-    </row>
-    <row r="175" spans="1:4">
-      <c r="A175" s="11" t="s">
-        <v>291</v>
-      </c>
-      <c r="B175" s="23" t="s">
-        <v>346</v>
-      </c>
-      <c r="C175" s="23" t="s">
-        <v>347</v>
-      </c>
-      <c r="D175" s="23" t="s"/>
     </row>
   </sheetData>
 </worksheet>

--- a/resources/国际化专业术语词典.xlsx
+++ b/resources/国际化专业术语词典.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="370" uniqueCount="370">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="376" uniqueCount="376">
   <si>
     <t/>
   </si>
@@ -1123,6 +1123,24 @@
   </si>
   <si>
     <t>VDC</t>
+  </si>
+  <si>
+    <t>精简管理</t>
+  </si>
+  <si>
+    <t>完全管理</t>
+  </si>
+  <si>
+    <t>特权密码</t>
+  </si>
+  <si>
+    <t>Simplified Management</t>
+  </si>
+  <si>
+    <t>Complete Management</t>
+  </si>
+  <si>
+    <t>Enable Password</t>
   </si>
 </sst>
 </file>
@@ -2689,21 +2707,39 @@
       <c r="D90" s="5" t="s"/>
     </row>
     <row r="91" spans="1:4">
-      <c r="A91" s="10" t="s"/>
-      <c r="B91" s="10" t="s"/>
-      <c r="C91" s="10" t="s"/>
+      <c r="A91" s="10" t="s">
+        <v>168</v>
+      </c>
+      <c r="B91" s="10" t="s">
+        <v>370</v>
+      </c>
+      <c r="C91" s="10" t="s">
+        <v>373</v>
+      </c>
       <c r="D91" s="10" t="s"/>
     </row>
     <row r="92" spans="1:4">
-      <c r="A92" s="11" t="s"/>
-      <c r="B92" s="11" t="s"/>
-      <c r="C92" s="11" t="s"/>
+      <c r="A92" s="11" t="s">
+        <v>168</v>
+      </c>
+      <c r="B92" s="11" t="s">
+        <v>371</v>
+      </c>
+      <c r="C92" s="11" t="s">
+        <v>374</v>
+      </c>
       <c r="D92" s="11" t="s"/>
     </row>
     <row r="93" spans="1:4">
-      <c r="A93" s="11" t="s"/>
-      <c r="B93" s="11" t="s"/>
-      <c r="C93" s="11" t="s"/>
+      <c r="A93" s="11" t="s">
+        <v>168</v>
+      </c>
+      <c r="B93" s="11" t="s">
+        <v>372</v>
+      </c>
+      <c r="C93" s="11" t="s">
+        <v>375</v>
+      </c>
       <c r="D93" s="11" t="s"/>
     </row>
     <row r="94" spans="1:4">
@@ -3669,5 +3705,6 @@
       <c r="D174" s="23" t="s"/>
     </row>
   </sheetData>
+  <autoFilter ref="A1:D174"/>
 </worksheet>
 </file>